--- a/ARM Functions/Other Mechanics/My Tracking TM HM Expansion.xlsx
+++ b/ARM Functions/Other Mechanics/My Tracking TM HM Expansion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Other Mechanics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{758C0724-1157-4BDD-9FB9-470BEC489F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C34A67-E43D-4370-A4F5-DAF3CFB004E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16457" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16457" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edited Table of TMs" sheetId="5" r:id="rId1"/>
@@ -8371,57 +8371,59 @@
           </cell>
         </row>
         <row r="117">
-          <cell r="B117"/>
-          <cell r="C117">
-            <v>0</v>
+          <cell r="B117" t="str">
+            <v>Aqua Fang</v>
+          </cell>
+          <cell r="C117" t="str">
+            <v>Water</v>
           </cell>
         </row>
         <row r="118">
           <cell r="B118"/>
-          <cell r="C118">
-            <v>0</v>
+          <cell r="C118" t="e">
+            <v>#N/A</v>
           </cell>
         </row>
         <row r="119">
           <cell r="B119"/>
-          <cell r="C119">
-            <v>0</v>
+          <cell r="C119" t="e">
+            <v>#N/A</v>
           </cell>
         </row>
         <row r="120">
           <cell r="B120"/>
-          <cell r="C120">
-            <v>0</v>
+          <cell r="C120" t="e">
+            <v>#N/A</v>
           </cell>
         </row>
         <row r="121">
           <cell r="B121"/>
-          <cell r="C121">
-            <v>0</v>
+          <cell r="C121" t="e">
+            <v>#N/A</v>
           </cell>
         </row>
         <row r="122">
           <cell r="B122"/>
-          <cell r="C122">
-            <v>0</v>
+          <cell r="C122" t="e">
+            <v>#N/A</v>
           </cell>
         </row>
         <row r="123">
           <cell r="B123"/>
-          <cell r="C123">
-            <v>0</v>
+          <cell r="C123" t="e">
+            <v>#N/A</v>
           </cell>
         </row>
         <row r="124">
           <cell r="B124"/>
-          <cell r="C124">
-            <v>0</v>
+          <cell r="C124" t="e">
+            <v>#N/A</v>
           </cell>
         </row>
         <row r="125">
           <cell r="B125"/>
-          <cell r="C125">
-            <v>0</v>
+          <cell r="C125" t="e">
+            <v>#N/A</v>
           </cell>
         </row>
         <row r="126">
@@ -8432,20 +8434,20 @@
         </row>
         <row r="127">
           <cell r="B127"/>
-          <cell r="C127">
-            <v>0</v>
+          <cell r="C127" t="e">
+            <v>#N/A</v>
           </cell>
         </row>
         <row r="128">
           <cell r="B128"/>
-          <cell r="C128">
-            <v>0</v>
+          <cell r="C128" t="e">
+            <v>#N/A</v>
           </cell>
         </row>
         <row r="129">
           <cell r="B129"/>
-          <cell r="C129">
-            <v>0</v>
+          <cell r="C129" t="e">
+            <v>#N/A</v>
           </cell>
         </row>
         <row r="130">
@@ -8859,7 +8861,7 @@
       </sheetData>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -14666,8 +14668,8 @@
         <f>_xlfn.XLOOKUP(L117,'Default Lists'!G:G,'Default Lists'!F:F,"")</f>
         <v>4301</v>
       </c>
-      <c r="L118" s="2">
-        <v>0</v>
+      <c r="L118" s="2" t="str">
+        <v>Water</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.45">
@@ -14711,10 +14713,10 @@
       </c>
       <c r="K119" s="2" t="str">
         <f>_xlfn.XLOOKUP(L118,'Default Lists'!G:G,'Default Lists'!F:F,"")</f>
-        <v/>
-      </c>
-      <c r="L119" s="2">
-        <v>0</v>
+        <v>3D01</v>
+      </c>
+      <c r="L119" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.45">
@@ -14753,12 +14755,12 @@
         <f t="shared" si="13"/>
         <v>004BD04E</v>
       </c>
-      <c r="K120" s="2" t="str">
+      <c r="K120" s="2" t="e">
         <f>_xlfn.XLOOKUP(L119,'Default Lists'!G:G,'Default Lists'!F:F,"")</f>
-        <v/>
-      </c>
-      <c r="L120" s="2">
-        <v>0</v>
+        <v>#N/A</v>
+      </c>
+      <c r="L120" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.45">
@@ -14797,12 +14799,12 @@
         <f t="shared" si="13"/>
         <v>004BD050</v>
       </c>
-      <c r="K121" s="2" t="str">
+      <c r="K121" s="2" t="e">
         <f>_xlfn.XLOOKUP(L120,'Default Lists'!G:G,'Default Lists'!F:F,"")</f>
-        <v/>
-      </c>
-      <c r="L121" s="2">
-        <v>0</v>
+        <v>#N/A</v>
+      </c>
+      <c r="L121" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.45">
@@ -14841,12 +14843,12 @@
         <f t="shared" si="13"/>
         <v>004BD052</v>
       </c>
-      <c r="K122" s="2" t="str">
+      <c r="K122" s="2" t="e">
         <f>_xlfn.XLOOKUP(L121,'Default Lists'!G:G,'Default Lists'!F:F,"")</f>
-        <v/>
-      </c>
-      <c r="L122" s="2">
-        <v>0</v>
+        <v>#N/A</v>
+      </c>
+      <c r="L122" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.45">
@@ -14885,12 +14887,12 @@
         <f t="shared" si="13"/>
         <v>004BD054</v>
       </c>
-      <c r="K123" s="2" t="str">
+      <c r="K123" s="2" t="e">
         <f>_xlfn.XLOOKUP(L122,'Default Lists'!G:G,'Default Lists'!F:F,"")</f>
-        <v/>
-      </c>
-      <c r="L123" s="2">
-        <v>0</v>
+        <v>#N/A</v>
+      </c>
+      <c r="L123" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.45">
@@ -14929,12 +14931,12 @@
         <f t="shared" si="13"/>
         <v>004BD056</v>
       </c>
-      <c r="K124" s="2" t="str">
+      <c r="K124" s="2" t="e">
         <f>_xlfn.XLOOKUP(L123,'Default Lists'!G:G,'Default Lists'!F:F,"")</f>
-        <v/>
-      </c>
-      <c r="L124" s="2">
-        <v>0</v>
+        <v>#N/A</v>
+      </c>
+      <c r="L124" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.45">
@@ -14976,12 +14978,12 @@
         <f t="shared" si="13"/>
         <v>004BD058</v>
       </c>
-      <c r="K125" s="2" t="str">
+      <c r="K125" s="2" t="e">
         <f>_xlfn.XLOOKUP(L124,'Default Lists'!G:G,'Default Lists'!F:F,"")</f>
-        <v/>
-      </c>
-      <c r="L125" s="2">
-        <v>0</v>
+        <v>#N/A</v>
+      </c>
+      <c r="L125" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.45">
@@ -15023,12 +15025,12 @@
         <f t="shared" si="13"/>
         <v>004BD05A</v>
       </c>
-      <c r="K126" s="2" t="str">
+      <c r="K126" s="2" t="e">
         <f>_xlfn.XLOOKUP(L125,'Default Lists'!G:G,'Default Lists'!F:F,"")</f>
-        <v/>
-      </c>
-      <c r="L126" s="2">
-        <v>0</v>
+        <v>#N/A</v>
+      </c>
+      <c r="L126" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.45">
@@ -15070,9 +15072,9 @@
         <f t="shared" si="13"/>
         <v>004BD05C</v>
       </c>
-      <c r="K127" s="2" t="str">
+      <c r="K127" s="2" t="e">
         <f>_xlfn.XLOOKUP(L126,'Default Lists'!G:G,'Default Lists'!F:F,"")</f>
-        <v/>
+        <v>#N/A</v>
       </c>
       <c r="L127" s="2">
         <v>0</v>
@@ -15121,8 +15123,8 @@
         <f>_xlfn.XLOOKUP(L127,'Default Lists'!G:G,'Default Lists'!F:F,"")</f>
         <v/>
       </c>
-      <c r="L128" s="2">
-        <v>0</v>
+      <c r="L128" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.45">
@@ -15164,12 +15166,12 @@
         <f t="shared" si="13"/>
         <v>004BD060</v>
       </c>
-      <c r="K129" s="2" t="str">
+      <c r="K129" s="2" t="e">
         <f>_xlfn.XLOOKUP(L128,'Default Lists'!G:G,'Default Lists'!F:F,"")</f>
-        <v/>
-      </c>
-      <c r="L129" s="2">
-        <v>0</v>
+        <v>#N/A</v>
+      </c>
+      <c r="L129" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.45">
@@ -15211,12 +15213,12 @@
         <f t="shared" si="13"/>
         <v>004BD062</v>
       </c>
-      <c r="K130" s="2" t="str">
+      <c r="K130" s="2" t="e">
         <f>_xlfn.XLOOKUP(L129,'Default Lists'!G:G,'Default Lists'!F:F,"")</f>
-        <v/>
-      </c>
-      <c r="L130" s="2">
-        <v>0</v>
+        <v>#N/A</v>
+      </c>
+      <c r="L130" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.45">
@@ -15258,9 +15260,9 @@
         <f t="shared" si="13"/>
         <v>004BD064</v>
       </c>
-      <c r="K131" s="2" t="str">
+      <c r="K131" s="2" t="e">
         <f>_xlfn.XLOOKUP(L130,'Default Lists'!G:G,'Default Lists'!F:F,"")</f>
-        <v/>
+        <v>#N/A</v>
       </c>
       <c r="L131" s="2" t="str">
         <v>Normal</v>
